--- a/public/forms/16.xlsx
+++ b/public/forms/16.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/689d1a227c82b3ba/Documents/cuenta cobro/enero/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\victor\proyectos\viva\vivapay\public\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{FA7B8B7C-CA5E-42D6-965E-57703659FF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3120A3A2-7252-46DD-8634-922984D1C0B2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38B0531-4E61-46BB-9017-8D46919BDA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="359" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="359" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GFR-FO-16" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
   <si>
     <t>AUTORIZACIÓN DE PAGO ORDENADOR DEL GASTO</t>
   </si>
@@ -55,16 +55,10 @@
     <t>CONTRATISTA:</t>
   </si>
   <si>
-    <t>VICTOR MANUEL CORDOBA CORDOBA</t>
-  </si>
-  <si>
     <t>CC/NIT</t>
   </si>
   <si>
     <t>No CONTRATO/CONVENIO:</t>
-  </si>
-  <si>
-    <t>CPS-99-2026</t>
   </si>
   <si>
     <t>No DISPONIBILIDAD:</t>
@@ -197,16 +191,7 @@
     <t>Registre la cédula de ciudadanía del ordenador del gasto</t>
   </si>
   <si>
-    <t>Yo,   MARIA MARLENY OROZCO ZULUAGA</t>
-  </si>
-  <si>
-    <t>ADMINISTRATIVA Y FINANCIERA</t>
-  </si>
-  <si>
-    <t>119 del 20/01/2026</t>
-  </si>
-  <si>
-    <t>291 del  28/01/2026</t>
+    <t xml:space="preserve">yo </t>
   </si>
 </sst>
 </file>
@@ -654,29 +639,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -734,7 +696,30 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1185,17 +1170,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="63"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="57"/>
     </row>
     <row r="2" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
@@ -1221,7 +1206,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
@@ -1229,36 +1214,34 @@
       <c r="E4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
       <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="62"/>
     </row>
     <row r="6" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="68"/>
+      <c r="A6" s="60"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="62"/>
     </row>
     <row r="7" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
@@ -1272,23 +1255,19 @@
       <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="65"/>
-      <c r="C8" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="47"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="68"/>
       <c r="G8" s="21"/>
       <c r="H8" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="27">
-        <v>1000191780</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
@@ -1313,14 +1292,12 @@
       <c r="I10" s="29"/>
     </row>
     <row r="11" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="65"/>
-      <c r="C11" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="48"/>
+      <c r="A11" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="59"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
       <c r="E11" s="21"/>
       <c r="F11" s="21"/>
       <c r="G11" s="21"/>
@@ -1339,8 +1316,8 @@
       <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="64"/>
-      <c r="B13" s="65"/>
+      <c r="A13" s="58"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="30"/>
@@ -1350,14 +1327,12 @@
       <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="49"/>
+      <c r="A14" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="59"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
       <c r="G14" s="21"/>
@@ -1387,14 +1362,12 @@
       <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="49"/>
+      <c r="A17" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="59"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
       <c r="E17" s="30"/>
       <c r="F17" s="30"/>
       <c r="G17" s="21"/>
@@ -1413,14 +1386,12 @@
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="65"/>
-      <c r="C19" s="49">
-        <v>1</v>
-      </c>
-      <c r="D19" s="49"/>
+      <c r="A19" s="58" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="59"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
@@ -1453,14 +1424,12 @@
       <c r="W21" s="14"/>
     </row>
     <row r="22" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="64" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="65"/>
-      <c r="C22" s="69">
-        <v>112235</v>
-      </c>
-      <c r="D22" s="69"/>
+      <c r="A22" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="59"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
       <c r="E22" s="30"/>
       <c r="F22" s="30"/>
       <c r="G22" s="30"/>
@@ -1494,15 +1463,15 @@
       <c r="W24" s="14"/>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="56"/>
-      <c r="B25" s="57"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="58"/>
+      <c r="A25" s="50"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="52"/>
       <c r="W25" s="14"/>
     </row>
     <row r="26" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1512,51 +1481,51 @@
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="53"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="47"/>
       <c r="W26" s="14"/>
     </row>
     <row r="27" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="44"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
+      <c r="A27" s="65"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
       <c r="E27" s="24">
         <v>21954827</v>
       </c>
       <c r="F27" s="21"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="53"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="47"/>
       <c r="W27" s="14"/>
     </row>
     <row r="28" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B28" s="26"/>
       <c r="C28" s="26"/>
       <c r="E28" s="40" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F28" s="11"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="53"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="47"/>
       <c r="W28" s="14"/>
     </row>
     <row r="29" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
+      <c r="A29" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
       <c r="F29" s="12"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="55"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="49"/>
       <c r="W29" s="14"/>
     </row>
     <row r="30" spans="1:23" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -1584,29 +1553,29 @@
       <c r="W31" s="14"/>
     </row>
     <row r="32" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" s="60"/>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
+      <c r="A32" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
       <c r="W32" s="14"/>
     </row>
     <row r="33" spans="1:23" ht="156" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="60"/>
-      <c r="B33" s="60"/>
-      <c r="C33" s="60"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
-      <c r="I33" s="60"/>
+      <c r="A33" s="54"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
       <c r="W33" s="14"/>
     </row>
     <row r="34" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1619,13 +1588,13 @@
       <c r="G34" s="41"/>
       <c r="H34" s="41"/>
       <c r="I34" s="42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W34" s="14"/>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="I35" s="43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W35" s="14"/>
     </row>
@@ -1730,37 +1699,37 @@
     </row>
     <row r="69" spans="19:23" x14ac:dyDescent="0.25">
       <c r="T69" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W69" s="14"/>
     </row>
     <row r="70" spans="19:23" x14ac:dyDescent="0.25">
       <c r="S70" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T70" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W70" s="14"/>
     </row>
     <row r="71" spans="19:23" x14ac:dyDescent="0.25">
       <c r="S71" s="13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="T71" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W71" s="14"/>
     </row>
     <row r="72" spans="19:23" x14ac:dyDescent="0.25">
       <c r="T72" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="W72" s="14"/>
     </row>
     <row r="73" spans="19:23" x14ac:dyDescent="0.25">
       <c r="T73" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="W73" s="14"/>
     </row>
@@ -1769,7 +1738,7 @@
         <v>43101</v>
       </c>
       <c r="T74" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="W74" s="14"/>
     </row>
@@ -1778,7 +1747,7 @@
         <v>43102</v>
       </c>
       <c r="T75" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="W75" s="14"/>
     </row>
@@ -1787,7 +1756,7 @@
         <v>43103</v>
       </c>
       <c r="T76" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="W76" s="14"/>
     </row>
@@ -1796,7 +1765,7 @@
         <v>43104</v>
       </c>
       <c r="T77" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="W77" s="14"/>
     </row>
@@ -1805,7 +1774,7 @@
         <v>43105</v>
       </c>
       <c r="T78" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="W78" s="14"/>
     </row>
@@ -1814,7 +1783,7 @@
         <v>43106</v>
       </c>
       <c r="T79" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="W79" s="14"/>
     </row>
@@ -1823,7 +1792,7 @@
         <v>43107</v>
       </c>
       <c r="T80" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="W80" s="14"/>
     </row>
@@ -10918,6 +10887,11 @@
     <protectedRange sqref="E8:I21" name="Rango1"/>
   </protectedRanges>
   <mergeCells count="21">
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="G26:I29"/>
     <mergeCell ref="A25:I25"/>
@@ -10934,11 +10908,6 @@
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C14:D14"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E39:F39" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -10962,7 +10931,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="70" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" s="71"/>
     </row>
@@ -10972,106 +10941,106 @@
     </row>
     <row r="3" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="39" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -11084,6 +11053,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="54909ea9-b8a6-49fb-80e9-be6d07efd491">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0114b50f-9d75-4745-893c-845a73c5ba4a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006098FC569B2E844387057BC377073F07" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a1e562420dc294ed62ccd2f77b457a64">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="54909ea9-b8a6-49fb-80e9-be6d07efd491" xmlns:ns3="0114b50f-9d75-4745-893c-845a73c5ba4a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b191f6e8884aab5c11f83754b5d6b2f9" ns2:_="" ns3:_="">
     <xsd:import namespace="54909ea9-b8a6-49fb-80e9-be6d07efd491"/>
@@ -11314,17 +11294,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="54909ea9-b8a6-49fb-80e9-be6d07efd491">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0114b50f-9d75-4745-893c-845a73c5ba4a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11335,6 +11304,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A99CB1A2-A7E2-4D84-B4E5-F6BBE64677A3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="54909ea9-b8a6-49fb-80e9-be6d07efd491"/>
+    <ds:schemaRef ds:uri="0114b50f-9d75-4745-893c-845a73c5ba4a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C325436-DF0E-4EBC-9086-5A3494D0AB4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11353,23 +11339,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A99CB1A2-A7E2-4D84-B4E5-F6BBE64677A3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="54909ea9-b8a6-49fb-80e9-be6d07efd491"/>
-    <ds:schemaRef ds:uri="0114b50f-9d75-4745-893c-845a73c5ba4a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{187E9BE1-6BE5-4164-9CDD-CD83005FCAF7}">
   <ds:schemaRefs>
